--- a/revit/ArmadoTrabes_Insurgentes/Armado_trabes_Nivel_Techos_N11.xlsx
+++ b/revit/ArmadoTrabes_Insurgentes/Armado_trabes_Nivel_Techos_N11.xlsx
@@ -3478,7 +3478,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>T- EJE 3</t>
+          <t>T- EJE 3 [S2]</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>Plano: 15X80 con 3#8 (dos claros 11@10 @20 11@10; en el modelo son 3 tramos, se puso en cada uno) y 15X40 con 2#6 @10. | secciones: T- EJE 3 Seccion 2 + T- EJE 3 Seccion 1 (se arman juntas; los bastones pasan el cambio de sección)</t>
+          <t>En el plano son vigas separadas: 15X80 con 3#8 (S2) y 15X40 con 2#6 (S1); cada parte se arma aparte. | Plano: 15X80 con 3#8 (dos claros 11@10 @20 11@10; en el modelo son 3 tramos, se puso en cada uno) y 15X40 con 2#6 @10. | secciones: T- EJE 3 Seccion 2 + T- EJE 3 Seccion 1 (se arman juntas; los bastones pasan el cambio de sección)</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>T- EJE 3</t>
+          <t>T- EJE 3 [S2]</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>T- EJE 3</t>
+          <t>T- EJE 3 [S2]</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3665,20 +3665,20 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>T- EJE 3</t>
+          <t>T- EJE 3 [S1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>5 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -3716,7 +3716,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S51" s="2" t="n"/>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas: 15X80 con 3#8 (S2) y 15X40 con 2#6 (S1); cada parte se arma aparte.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3726,20 +3730,20 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>T- EJE 3</t>
+          <t>T- EJE 3 [S1]</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>5 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>6 (muro bajo la viga)</t>
+          <t>3 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -3787,20 +3791,20 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>T- EJE 3</t>
+          <t>T- EJE 3 [S1]</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>6 (muro bajo la viga)</t>
+          <t>3 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>7 (viga)</t>
+          <t>4 (viga)</t>
         </is>
       </c>
       <c r="F53" t="n">

--- a/revit/ArmadoTrabes_Insurgentes/Armado_trabes_Nivel_Techos_N11.xlsx
+++ b/revit/ArmadoTrabes_Insurgentes/Armado_trabes_Nivel_Techos_N11.xlsx
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>T- 7 (viga 1)</t>
+          <t>T- 7 (viga 1) [T1-3]</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>Plano: dos claros 11@10 @20 11@10 y uno @10; en el modelo son 3 tramos + 1: se puso 11@10 @20 11@10 en cada uno (no menos estribos que el plano). | 2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. | Plano: dos claros 11@10 @20 11@10 y uno @10; en el modelo son 3 tramos + 1: se puso 11@10 @20 11@10 en cada uno (no menos estribos que el plano). | 2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>T- 7 (viga 1)</t>
+          <t>T- 7 (viga 1) [T1-3]</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>T- 7 (viga 1)</t>
+          <t>T- 7 (viga 1) [T1-3]</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2177,20 +2177,20 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>T- 7 (viga 1)</t>
+          <t>T- 7 (viga 1) [T4]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>5 (muro)</t>
+          <t>2 (muro)</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -2228,7 +2228,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S27" s="2" t="n"/>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2238,7 +2242,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>T- 7 (viga 2)</t>
+          <t>T- 7 (viga 2) [T1-3]</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2289,7 +2293,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S28" s="2" t="n"/>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2299,7 +2307,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>T- 7 (viga 2)</t>
+          <t>T- 7 (viga 2) [T1-3]</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2360,7 +2368,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>T- 7 (viga 2)</t>
+          <t>T- 7 (viga 2) [T1-3]</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2421,20 +2429,20 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>T- 7 (viga 2)</t>
+          <t>T- 7 (viga 2) [T4]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>1 (viga)</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>5 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -2472,7 +2480,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S31" s="2" t="n"/>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -5238,7 +5250,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>T-EJE K</t>
+          <t>T-EJE K [T1]</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -5291,7 +5303,7 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>Tramo 1 (entre los dos muros) no viene detallado en el plano: se supuso @10.</t>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo 1 (entre los dos cajones) no viene detallado: se supuso @10. | Tramo 1 (entre los dos muros) no viene detallado en el plano: se supuso @10.</t>
         </is>
       </c>
     </row>
@@ -5303,20 +5315,20 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>T-EJE K</t>
+          <t>T-EJE K [T2-6]</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>2 (muro bajo la viga)</t>
+          <t>1 (muro bajo la viga)</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>3 (viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -5358,7 +5370,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S77" s="2" t="n"/>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo 1 (entre los dos cajones) no viene detallado: se supuso @10.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5368,20 +5384,20 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>T-EJE K</t>
+          <t>T-EJE K [T2-6]</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
+          <t>2 (viga)</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
           <t>3 (viga)</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>4 (viga)</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -5437,20 +5453,20 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>T-EJE K</t>
+          <t>T-EJE K [T2-6]</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
+          <t>3 (viga)</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
           <t>4 (viga)</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>5 (viga)</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -5498,20 +5514,20 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>T-EJE K</t>
+          <t>T-EJE K [T2-6]</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
+          <t>4 (viga)</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
           <t>5 (viga)</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>6 (viga)</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -5559,20 +5575,20 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>T-EJE K</t>
+          <t>T-EJE K [T2-6]</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
+          <t>5 (viga)</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
           <t>6 (viga)</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>7 (viga)</t>
         </is>
       </c>
       <c r="F81" t="n">
